--- a/input/Timetable.xlsx
+++ b/input/Timetable.xlsx
@@ -1,74 +1,146 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\hussamuddin\Exam_Seating_Arrangement-main\input\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9615"/>
   </bookViews>
   <sheets>
-    <sheet name="Timetable" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Timetable" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Timetable'!$A$6:$C$10</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Timetable'!$1:$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Timetable'!$A$1:$C$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Timetable!$A$6:$C$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Timetable!$A$1:$C$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Timetable!$1:$6</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+  <si>
+    <t>Exam Date</t>
+  </si>
+  <si>
+    <t>Exam Name</t>
+  </si>
+  <si>
+    <t>Month / Year</t>
+  </si>
+  <si>
+    <t>October 2026</t>
+  </si>
+  <si>
+    <t>Timing</t>
+  </si>
+  <si>
+    <t>9:00 a.m. - 10:00 a.m.</t>
+  </si>
+  <si>
+    <t>Example exam day — edit the details above and the participating exams below.</t>
+  </si>
+  <si>
+    <t>Class</t>
+  </si>
+  <si>
+    <t>Semester</t>
+  </si>
+  <si>
+    <t>Subject</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>Cost Accounting</t>
+  </si>
+  <si>
+    <t>SYBMS (Finance)</t>
+  </si>
+  <si>
+    <t>III</t>
+  </si>
+  <si>
+    <t>FYCS</t>
+  </si>
+  <si>
+    <t>DBMS</t>
+  </si>
+  <si>
+    <t>Regular/Additional Examination</t>
+  </si>
+  <si>
+    <t>TYCS</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>IKS (Major)</t>
+  </si>
+  <si>
+    <t>SYBMS (Marketing)</t>
+  </si>
+  <si>
+    <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
-  </numFmts>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF203040"/>
       <name val="Calibri"/>
-      <color rgb="00203040"/>
-      <sz val="12"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="12"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
       <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0093721B"/>
+        <fgColor rgb="FF93721B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F6FA"/>
+        <fgColor rgb="FFF2F6FA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,118 +154,60 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BCC9D4"/>
+        <color rgb="FFBCC9D4"/>
       </left>
       <right style="thin">
-        <color rgb="00BCC9D4"/>
+        <color rgb="FFBCC9D4"/>
       </right>
       <top style="thin">
-        <color rgb="00BCC9D4"/>
+        <color rgb="FFBCC9D4"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BCC9D4"/>
+        <color rgb="FFBCC9D4"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="14" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -481,161 +495,114 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Exam Date</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n">
+    <row r="1" spans="1:3" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7">
         <v>46304</v>
       </c>
-      <c r="C1" s="3" t="n"/>
-    </row>
-    <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Exam Name</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>F.Y. - Regular/Additional Examination</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="n"/>
-    </row>
-    <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Month / Year</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>October 2026</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n"/>
-    </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Timing</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>9:00 a.m. - 10:00 a.m.</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n"/>
-    </row>
-    <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Example exam day — edit the details above and the participating exams below.</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-    </row>
-    <row r="6" ht="44" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Class</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Semester</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Subject</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="44" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>F.Y.B.Com</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Cost Accounting</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="44" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Database Management</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="44" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Physics</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="44" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
+      <c r="C1" s="5"/>
+    </row>
+    <row r="2" spans="1:3" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="5"/>
+    </row>
+    <row r="3" spans="1:3" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="5"/>
+    </row>
+    <row r="4" spans="1:3" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="5"/>
+    </row>
+    <row r="5" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+    </row>
+    <row r="6" spans="1:3" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -648,6 +615,6 @@
     <mergeCell ref="B4:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
 </worksheet>
 </file>
--- a/input/Timetable.xlsx
+++ b/input/Timetable.xlsx
@@ -1,129 +1,53 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\hussamuddin\Exam_Seating_Arrangement-main\input\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9615"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9615" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Timetable" sheetId="1" r:id="rId1"/>
+    <sheet name="Timetable" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Timetable!$A$6:$C$10</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Timetable!$A$1:$C$10</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">Timetable!$1:$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Timetable'!$A$6:$C$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Timetable'!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Timetable'!$A$1:$C$10</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
-  <si>
-    <t>Exam Date</t>
-  </si>
-  <si>
-    <t>Exam Name</t>
-  </si>
-  <si>
-    <t>Month / Year</t>
-  </si>
-  <si>
-    <t>October 2026</t>
-  </si>
-  <si>
-    <t>Timing</t>
-  </si>
-  <si>
-    <t>9:00 a.m. - 10:00 a.m.</t>
-  </si>
-  <si>
-    <t>Example exam day — edit the details above and the participating exams below.</t>
-  </si>
-  <si>
-    <t>Class</t>
-  </si>
-  <si>
-    <t>Semester</t>
-  </si>
-  <si>
-    <t>Subject</t>
-  </si>
-  <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>Cost Accounting</t>
-  </si>
-  <si>
-    <t>SYBMS (Finance)</t>
-  </si>
-  <si>
-    <t>III</t>
-  </si>
-  <si>
-    <t>FYCS</t>
-  </si>
-  <si>
-    <t>DBMS</t>
-  </si>
-  <si>
-    <t>Regular/Additional Examination</t>
-  </si>
-  <si>
-    <t>TYCS</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>IKS (Major)</t>
-  </si>
-  <si>
-    <t>SYBMS (Marketing)</t>
-  </si>
-  <si>
-    <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <color rgb="FF203040"/>
       <sz val="12"/>
-      <color rgb="FF203040"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="12"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
       <sz val="12"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -172,42 +96,101 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -495,114 +478,155 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7">
+    <row r="1" ht="26.1" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Exam Date</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="n">
         <v>46304</v>
       </c>
-      <c r="C1" s="5"/>
-    </row>
-    <row r="2" spans="1:3" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="5"/>
-    </row>
-    <row r="3" spans="1:3" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="5"/>
-    </row>
-    <row r="4" spans="1:3" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="5"/>
-    </row>
-    <row r="5" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-    </row>
-    <row r="6" spans="1:3" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>21</v>
+    </row>
+    <row r="2" ht="26.1" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Exam Name</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Regular/Additional Examination</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26.1" customHeight="1">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Month / Year</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26.1" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Timing</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>9:00 a.m. - 10:00 a.m.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="33.95" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Example exam day — edit the details above and the participating exams below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44.1" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Semester</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44.1" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>SYBMS (Finance)</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Cost Accounting I (Minor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="44.1" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>FYCS</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>DBMS (Major)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="44.1" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>TYCS</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>IKS (Major)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44.1" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SYBMS (Marketing)</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -615,6 +639,6 @@
     <mergeCell ref="B4:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0"/>
 </worksheet>
 </file>